--- a/trunk/plan/excel/技能表.xlsx
+++ b/trunk/plan/excel/技能表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25440" windowHeight="3960"/>
+    <workbookView windowHeight="17175"/>
   </bookViews>
   <sheets>
     <sheet name="SkillCFG" sheetId="1" r:id="rId1"/>
@@ -120,14 +120,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -583,148 +576,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>

--- a/trunk/plan/excel/技能表.xlsx
+++ b/trunk/plan/excel/技能表.xlsx
@@ -4,10 +4,11 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17175"/>
+    <workbookView windowWidth="25185" windowHeight="7995"/>
   </bookViews>
   <sheets>
     <sheet name="SkillCFG" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -26,8 +27,62 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Administrator</author>
+  </authors>
+  <commentList>
+    <comment ref="C1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+敌方单体，敌方群体，我当单体，自身，我方群体，全体</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+消耗能量</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="31">
   <si>
     <t>ID</t>
   </si>
@@ -35,6 +90,9 @@
     <t>Name</t>
   </si>
   <si>
+    <t>TargetType</t>
+  </si>
+  <si>
     <t>Type</t>
   </si>
   <si>
@@ -47,7 +105,7 @@
     <t>Cost</t>
   </si>
   <si>
-    <t>EffectIds</t>
+    <t>BuffIds</t>
   </si>
   <si>
     <t>Level</t>
@@ -74,7 +132,7 @@
     <t>主动</t>
   </si>
   <si>
-    <t>发射火球造成伤害</t>
+    <t>发射火球造成瞬间伤害，并对单位施加一个持续灼烧的状态，持续5秒</t>
   </si>
   <si>
     <t>1,2</t>
@@ -83,13 +141,13 @@
     <t>skill_fireball</t>
   </si>
   <si>
-    <t>治疗术</t>
-  </si>
-  <si>
-    <t>恢复生命值</t>
-  </si>
-  <si>
-    <t>3</t>
+    <t>愈合术</t>
+  </si>
+  <si>
+    <t>恢复生命值，并在后续时间内为单位进行回血，持续5秒</t>
+  </si>
+  <si>
+    <t>3,4</t>
   </si>
   <si>
     <t>skill_heal</t>
@@ -101,13 +159,22 @@
     <t>被动</t>
   </si>
   <si>
-    <t>提升攻击力</t>
-  </si>
-  <si>
-    <t>4,5</t>
+    <t>提升攻击力。提升20%物理攻击力，并降低5%的物理防御护甲</t>
+  </si>
+  <si>
+    <t>5,6</t>
   </si>
   <si>
     <t>skill_berserk</t>
+  </si>
+  <si>
+    <t>蓝霸符</t>
+  </si>
+  <si>
+    <t>在施法时有20%概率进行使概率蓝量增加1点</t>
+  </si>
+  <si>
+    <t>技能设计是一种无锁战斗设计，选中单位有TargetType进行选中，技能效果由Buff列表控制</t>
   </si>
 </sst>
 </file>
@@ -120,7 +187,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -271,6 +338,17 @@
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="33">
@@ -1069,10 +1147,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4"/>
+  <dimension ref="A1:J6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5"/>
+  <cols>
+    <col min="3" max="3" width="11.5" customWidth="1"/>
+    <col min="5" max="5" width="64" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:10">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1100,121 +1182,177 @@
       <c r="I1" t="s">
         <v>8</v>
       </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E2" t="s">
         <v>11</v>
       </c>
       <c r="F2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="I2" t="s">
         <v>10</v>
       </c>
+      <c r="J2" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:10">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" t="s">
         <v>14</v>
       </c>
       <c r="D3" t="s">
         <v>15</v>
       </c>
-      <c r="E3">
+      <c r="E3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3">
         <v>5</v>
       </c>
-      <c r="F3">
+      <c r="G3">
         <v>10</v>
       </c>
-      <c r="G3" t="s">
-        <v>16</v>
-      </c>
-      <c r="H3">
+      <c r="H3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I3">
         <v>1</v>
       </c>
-      <c r="I3" t="s">
-        <v>17</v>
+      <c r="J3" t="s">
+        <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:10">
       <c r="A4">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E4">
+        <v>15</v>
+      </c>
+      <c r="E4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F4">
         <v>8</v>
       </c>
-      <c r="F4">
+      <c r="G4">
         <v>15</v>
       </c>
-      <c r="G4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H4">
+      <c r="H4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I4">
         <v>1</v>
       </c>
-      <c r="I4" t="s">
-        <v>21</v>
+      <c r="J4" t="s">
+        <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:10">
       <c r="A5">
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" t="s">
         <v>23</v>
       </c>
       <c r="D5" t="s">
         <v>24</v>
       </c>
-      <c r="E5">
-        <v>0</v>
+      <c r="E5" t="s">
+        <v>25</v>
       </c>
       <c r="F5">
         <v>0</v>
       </c>
-      <c r="G5" t="s">
-        <v>25</v>
-      </c>
-      <c r="H5">
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5" t="s">
+        <v>26</v>
+      </c>
+      <c r="I5">
         <v>1</v>
       </c>
-      <c r="I5" t="s">
-        <v>26</v>
+      <c r="J5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E6" t="s">
+        <v>29</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>7</v>
+      </c>
+      <c r="I6">
+        <v>1</v>
+      </c>
+      <c r="J6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <cols>
+    <col min="1" max="1" width="88.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>

--- a/trunk/plan/excel/技能表.xlsx
+++ b/trunk/plan/excel/技能表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25185" windowHeight="7995"/>
+    <workbookView windowWidth="27465" windowHeight="8655"/>
   </bookViews>
   <sheets>
     <sheet name="SkillCFG" sheetId="1" r:id="rId1"/>
@@ -82,7 +82,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="29">
   <si>
     <t>ID</t>
   </si>
@@ -144,7 +144,7 @@
     <t>愈合术</t>
   </si>
   <si>
-    <t>恢复生命值，并在后续时间内为单位进行回血，持续5秒</t>
+    <t>恢复生命值，并在后续时间内为随机友军单位进行回血，持续5秒</t>
   </si>
   <si>
     <t>3,4</t>
@@ -156,13 +156,7 @@
     <t>狂暴</t>
   </si>
   <si>
-    <t>被动</t>
-  </si>
-  <si>
-    <t>提升攻击力。提升20%物理攻击力，并降低5%的物理防御护甲</t>
-  </si>
-  <si>
-    <t>5,6</t>
+    <t>提升攻击力。提升自身20%物理攻击力，并降低5%的物理防御护甲</t>
   </si>
   <si>
     <t>skill_berserk</t>
@@ -1225,6 +1219,9 @@
       <c r="B3" t="s">
         <v>14</v>
       </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
       <c r="D3" t="s">
         <v>15</v>
       </c>
@@ -1232,10 +1229,10 @@
         <v>16</v>
       </c>
       <c r="F3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G3">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H3" t="s">
         <v>17</v>
@@ -1254,6 +1251,9 @@
       <c r="B4" t="s">
         <v>19</v>
       </c>
+      <c r="C4">
+        <v>2</v>
+      </c>
       <c r="D4" t="s">
         <v>15</v>
       </c>
@@ -1261,10 +1261,10 @@
         <v>20</v>
       </c>
       <c r="F4">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G4">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="H4" t="s">
         <v>21</v>
@@ -1283,26 +1283,29 @@
       <c r="B5" t="s">
         <v>23</v>
       </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
       <c r="D5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" t="s">
         <v>24</v>
-      </c>
-      <c r="E5" t="s">
-        <v>25</v>
       </c>
       <c r="F5">
         <v>0</v>
       </c>
       <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5" t="s">
-        <v>26</v>
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>5</v>
       </c>
       <c r="I5">
         <v>1</v>
       </c>
       <c r="J5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -1310,19 +1313,22 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>28</v>
+        <v>26</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
       </c>
       <c r="D6" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="E6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F6">
         <v>0</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6">
         <v>7</v>
@@ -1352,7 +1358,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>

--- a/trunk/plan/excel/技能表.xlsx
+++ b/trunk/plan/excel/技能表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27465" windowHeight="8655"/>
+    <workbookView windowWidth="30585" windowHeight="8985"/>
   </bookViews>
   <sheets>
     <sheet name="SkillCFG" sheetId="1" r:id="rId1"/>
@@ -51,7 +51,7 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-敌方单体，敌方群体，我当单体，自身，我方群体，全体</t>
+0.自身 1.敌方单体 敌方群体，我当单体，自身，我方群体，全体</t>
         </r>
       </text>
     </comment>

--- a/trunk/plan/excel/技能表.xlsx
+++ b/trunk/plan/excel/技能表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="30585" windowHeight="8985"/>
+    <workbookView windowHeight="17175"/>
   </bookViews>
   <sheets>
     <sheet name="SkillCFG" sheetId="1" r:id="rId1"/>

--- a/trunk/plan/excel/技能表.xlsx
+++ b/trunk/plan/excel/技能表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17175"/>
+    <workbookView windowWidth="22350" windowHeight="11055"/>
   </bookViews>
   <sheets>
     <sheet name="SkillCFG" sheetId="1" r:id="rId1"/>

--- a/trunk/plan/excel/技能表.xlsx
+++ b/trunk/plan/excel/技能表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22350" windowHeight="11055"/>
+    <workbookView windowWidth="27030" windowHeight="12825"/>
   </bookViews>
   <sheets>
     <sheet name="SkillCFG" sheetId="1" r:id="rId1"/>

--- a/trunk/plan/excel/技能表.xlsx
+++ b/trunk/plan/excel/技能表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27030" windowHeight="12825"/>
+    <workbookView windowWidth="24570" windowHeight="10290"/>
   </bookViews>
   <sheets>
     <sheet name="SkillCFG" sheetId="1" r:id="rId1"/>
@@ -82,7 +82,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="31">
   <si>
     <t>ID</t>
   </si>
@@ -166,6 +166,12 @@
   </si>
   <si>
     <t>在施法时有20%概率进行使概率蓝量增加1点</t>
+  </si>
+  <si>
+    <t>制裁</t>
+  </si>
+  <si>
+    <t>目标单位眩晕两回合，无法进行任何操作</t>
   </si>
   <si>
     <t>技能设计是一种无锁战斗设计，选中单位有TargetType进行选中，技能效果由Buff列表控制</t>
@@ -1141,8 +1147,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5"/>
+  <dimension ref="A1:J7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6"/>
   <cols>
     <col min="3" max="3" width="11.5" customWidth="1"/>
     <col min="5" max="5" width="64" customWidth="1"/>
@@ -1338,6 +1344,38 @@
       </c>
       <c r="J6" t="s">
         <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7" t="s">
+        <v>15</v>
+      </c>
+      <c r="E7" t="s">
+        <v>29</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7">
+        <v>6</v>
+      </c>
+      <c r="I7">
+        <v>1</v>
+      </c>
+      <c r="J7" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -1358,7 +1396,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
